--- a/outputs/ToT_(Labour/Cereal)_percentile_classification_matrix.xlsx
+++ b/outputs/ToT_(Labour/Cereal)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="136">
   <si>
     <t>2020 May</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Alarm</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>28%</t>
@@ -1246,13 +1249,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BW2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1473,13 +1476,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BW3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1700,13 +1703,13 @@
         <v>109</v>
       </c>
       <c r="BU4" t="s">
+        <v>114</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>126</v>
+      </c>
+      <c r="BW4" t="s">
         <v>113</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>125</v>
-      </c>
-      <c r="BW4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1927,13 +1930,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -2154,13 +2157,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2333,61 +2336,61 @@
         <v>108</v>
       </c>
       <c r="BE7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BF7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BG7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BH7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BI7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BJ7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BK7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BL7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BM7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BN7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BO7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BP7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BQ7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BR7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BS7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BT7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BU7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2608,13 +2611,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2835,13 +2838,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
+        <v>117</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>128</v>
+      </c>
+      <c r="BW9" t="s">
         <v>116</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>127</v>
-      </c>
-      <c r="BW9" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -3062,13 +3065,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BW10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3289,13 +3292,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3516,13 +3519,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3743,13 +3746,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BW13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3970,13 +3973,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4197,13 +4200,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4424,13 +4427,13 @@
         <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BV16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BW16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4651,13 +4654,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BW17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4878,13 +4881,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BW18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -5060,16 +5063,16 @@
         <v>108</v>
       </c>
       <c r="BF19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BG19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BH19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BI19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BJ19" t="s">
         <v>108</v>
@@ -5087,31 +5090,31 @@
         <v>108</v>
       </c>
       <c r="BO19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BP19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BQ19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BR19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BS19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BT19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BU19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5332,13 +5335,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BV20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5559,13 +5562,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW21" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5786,13 +5789,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BV22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -6013,13 +6016,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BW23" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6240,13 +6243,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV24" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BW24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6467,13 +6470,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BV25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BW25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6511,7 +6514,7 @@
         <v>108</v>
       </c>
       <c r="L26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M26" t="s">
         <v>108</v>
@@ -6550,157 +6553,157 @@
         <v>108</v>
       </c>
       <c r="Y26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Z26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AA26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AB26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AC26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AD26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AE26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AF26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AH26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AI26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AJ26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AK26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AL26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AM26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AN26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AO26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AP26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AQ26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AR26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AS26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AT26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AU26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AV26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AW26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AX26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AY26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AZ26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BA26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BB26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BC26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BD26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BE26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BF26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BG26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BH26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BI26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BJ26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BK26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BL26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BM26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BN26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BO26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BP26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BQ26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BR26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BS26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BT26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BU26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BV26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BW26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6921,13 +6924,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="BW27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7148,13 +7151,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV28" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7375,13 +7378,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7602,13 +7605,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BV30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7829,13 +7832,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV31" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -8056,13 +8059,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BV32" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW32" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8283,13 +8286,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BW33" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8510,13 +8513,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BV34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW34" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ToT_(Labour/Cereal)_percentile_classification_matrix.xlsx
+++ b/outputs/ToT_(Labour/Cereal)_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="111">
   <si>
     <t>2020 May</t>
   </si>
@@ -343,85 +343,10 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>No data</t>
   </si>
   <si>
-    <t>28%</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>32%</t>
-  </si>
-  <si>
-    <t>27%</t>
-  </si>
-  <si>
-    <t>31%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>23%</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>37%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>38%</t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
-    <t>34%</t>
-  </si>
-  <si>
-    <t>42%</t>
   </si>
 </sst>
 </file>
@@ -1081,64 +1006,64 @@
         <v>108</v>
       </c>
       <c r="Q2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK2" t="s">
         <v>108</v>
@@ -1147,7 +1072,7 @@
         <v>108</v>
       </c>
       <c r="AM2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN2" t="s">
         <v>108</v>
@@ -1249,13 +1174,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV2" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="BW2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1296,73 +1221,73 @@
         <v>108</v>
       </c>
       <c r="M3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ3" t="s">
         <v>108</v>
@@ -1476,13 +1401,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV3" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BW3" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1541,7 +1466,7 @@
         <v>108</v>
       </c>
       <c r="S4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T4" t="s">
         <v>108</v>
@@ -1559,58 +1484,58 @@
         <v>108</v>
       </c>
       <c r="Y4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO4" t="s">
         <v>108</v>
       </c>
       <c r="AP4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ4" t="s">
         <v>108</v>
@@ -1691,25 +1616,25 @@
         <v>108</v>
       </c>
       <c r="BQ4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BR4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BS4" t="s">
         <v>108</v>
       </c>
       <c r="BT4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV4" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="BW4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1765,64 +1690,64 @@
         <v>108</v>
       </c>
       <c r="R5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL5" t="s">
         <v>108</v>
@@ -1924,19 +1849,19 @@
         <v>108</v>
       </c>
       <c r="BS5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT5" t="s">
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV5" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BW5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1947,7 +1872,7 @@
         <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
         <v>108</v>
@@ -1965,16 +1890,16 @@
         <v>108</v>
       </c>
       <c r="I6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s">
         <v>108</v>
@@ -1989,67 +1914,67 @@
         <v>108</v>
       </c>
       <c r="Q6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL6" t="s">
         <v>108</v>
@@ -2064,7 +1989,7 @@
         <v>108</v>
       </c>
       <c r="AP6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ6" t="s">
         <v>108</v>
@@ -2157,13 +2082,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BV6" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW6" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2225,172 +2150,172 @@
         <v>108</v>
       </c>
       <c r="T7" t="s">
+        <v>108</v>
+      </c>
+      <c r="U7" t="s">
+        <v>108</v>
+      </c>
+      <c r="V7" t="s">
+        <v>108</v>
+      </c>
+      <c r="W7" t="s">
+        <v>108</v>
+      </c>
+      <c r="X7" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>108</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>108</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>108</v>
+      </c>
+      <c r="BE7" t="s">
         <v>109</v>
       </c>
-      <c r="U7" t="s">
-        <v>110</v>
-      </c>
-      <c r="V7" t="s">
-        <v>110</v>
-      </c>
-      <c r="W7" t="s">
-        <v>110</v>
-      </c>
-      <c r="X7" t="s">
-        <v>110</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>110</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AH7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AK7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AL7" t="s">
+      <c r="BF7" t="s">
         <v>109</v>
       </c>
-      <c r="AM7" t="s">
+      <c r="BG7" t="s">
         <v>109</v>
       </c>
-      <c r="AN7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AO7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AP7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AQ7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AW7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AX7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AY7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AZ7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BA7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BB7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD7" t="s">
-        <v>108</v>
-      </c>
-      <c r="BE7" t="s">
-        <v>111</v>
-      </c>
-      <c r="BF7" t="s">
-        <v>111</v>
-      </c>
-      <c r="BG7" t="s">
-        <v>111</v>
-      </c>
       <c r="BH7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BI7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BJ7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BK7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BL7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BM7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BN7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BO7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BP7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BQ7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BR7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BS7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BT7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BU7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV7" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BW7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2428,85 +2353,85 @@
         <v>108</v>
       </c>
       <c r="L8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M8" t="s">
         <v>108</v>
       </c>
       <c r="N8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ8" t="s">
         <v>108</v>
       </c>
       <c r="AK8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM8" t="s">
         <v>108</v>
@@ -2611,13 +2536,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV8" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW8" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2625,7 +2550,7 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
         <v>108</v>
@@ -2664,70 +2589,70 @@
         <v>108</v>
       </c>
       <c r="O9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK9" t="s">
         <v>108</v>
@@ -2838,13 +2763,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV9" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW9" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2852,34 +2777,34 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H10" t="s">
         <v>108</v>
       </c>
       <c r="I10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L10" t="s">
         <v>108</v>
@@ -2897,55 +2822,55 @@
         <v>108</v>
       </c>
       <c r="Q10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH10" t="s">
         <v>108</v>
@@ -3065,13 +2990,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV10" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="BW10" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3079,7 +3004,7 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
         <v>108</v>
@@ -3100,10 +3025,10 @@
         <v>108</v>
       </c>
       <c r="I11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K11" t="s">
         <v>108</v>
@@ -3121,67 +3046,67 @@
         <v>108</v>
       </c>
       <c r="P11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK11" t="s">
         <v>108</v>
@@ -3262,7 +3187,7 @@
         <v>108</v>
       </c>
       <c r="BK11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BL11" t="s">
         <v>108</v>
@@ -3292,13 +3217,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV11" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW11" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3333,88 +3258,88 @@
         <v>108</v>
       </c>
       <c r="K12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M12" t="s">
         <v>108</v>
       </c>
       <c r="N12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R12" t="s">
         <v>108</v>
       </c>
       <c r="S12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM12" t="s">
         <v>108</v>
@@ -3519,13 +3444,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BV12" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BW12" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3581,67 +3506,67 @@
         <v>108</v>
       </c>
       <c r="R13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK13" t="s">
         <v>108</v>
       </c>
       <c r="AL13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM13" t="s">
         <v>108</v>
@@ -3746,13 +3671,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV13" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BW13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3805,61 +3730,61 @@
         <v>108</v>
       </c>
       <c r="Q14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ14" t="s">
         <v>108</v>
@@ -3871,31 +3796,31 @@
         <v>108</v>
       </c>
       <c r="AM14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS14" t="s">
         <v>108</v>
       </c>
       <c r="AT14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AU14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV14" t="s">
         <v>108</v>
@@ -3973,13 +3898,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BV14" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW14" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -3987,10 +3912,10 @@
         <v>88</v>
       </c>
       <c r="B15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -4038,64 +3963,64 @@
         <v>108</v>
       </c>
       <c r="S15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM15" t="s">
         <v>108</v>
@@ -4200,13 +4125,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV15" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BW15" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4250,82 +4175,82 @@
         <v>108</v>
       </c>
       <c r="N16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="O16" t="s">
         <v>108</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK16" t="s">
         <v>108</v>
       </c>
       <c r="AL16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN16" t="s">
         <v>108</v>
@@ -4427,13 +4352,13 @@
         <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BV16" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BW16" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4489,64 +4414,64 @@
         <v>108</v>
       </c>
       <c r="R17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL17" t="s">
         <v>108</v>
@@ -4654,13 +4579,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV17" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BW17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4713,10 +4638,10 @@
         <v>108</v>
       </c>
       <c r="Q18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S18" t="s">
         <v>108</v>
@@ -4728,55 +4653,55 @@
         <v>108</v>
       </c>
       <c r="V18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM18" t="s">
         <v>108</v>
@@ -4881,13 +4806,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV18" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BW18" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4904,217 +4829,217 @@
         <v>108</v>
       </c>
       <c r="E19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H19" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" t="s">
+        <v>108</v>
+      </c>
+      <c r="K19" t="s">
+        <v>108</v>
+      </c>
+      <c r="L19" t="s">
+        <v>108</v>
+      </c>
+      <c r="M19" t="s">
+        <v>108</v>
+      </c>
+      <c r="N19" t="s">
+        <v>108</v>
+      </c>
+      <c r="O19" t="s">
+        <v>108</v>
+      </c>
+      <c r="P19" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>108</v>
+      </c>
+      <c r="R19" t="s">
+        <v>108</v>
+      </c>
+      <c r="S19" t="s">
+        <v>108</v>
+      </c>
+      <c r="T19" t="s">
+        <v>108</v>
+      </c>
+      <c r="U19" t="s">
+        <v>108</v>
+      </c>
+      <c r="V19" t="s">
+        <v>108</v>
+      </c>
+      <c r="W19" t="s">
+        <v>108</v>
+      </c>
+      <c r="X19" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AU19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BE19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BF19" t="s">
         <v>109</v>
       </c>
-      <c r="F19" t="s">
-        <v>110</v>
-      </c>
-      <c r="G19" t="s">
-        <v>108</v>
-      </c>
-      <c r="H19" t="s">
-        <v>108</v>
-      </c>
-      <c r="I19" t="s">
-        <v>108</v>
-      </c>
-      <c r="J19" t="s">
-        <v>108</v>
-      </c>
-      <c r="K19" t="s">
-        <v>108</v>
-      </c>
-      <c r="L19" t="s">
-        <v>108</v>
-      </c>
-      <c r="M19" t="s">
-        <v>108</v>
-      </c>
-      <c r="N19" t="s">
-        <v>108</v>
-      </c>
-      <c r="O19" t="s">
+      <c r="BG19" t="s">
         <v>109</v>
       </c>
-      <c r="P19" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>110</v>
-      </c>
-      <c r="R19" t="s">
-        <v>110</v>
-      </c>
-      <c r="S19" t="s">
-        <v>110</v>
-      </c>
-      <c r="T19" t="s">
-        <v>110</v>
-      </c>
-      <c r="U19" t="s">
-        <v>110</v>
-      </c>
-      <c r="V19" t="s">
-        <v>110</v>
-      </c>
-      <c r="W19" t="s">
+      <c r="BH19" t="s">
         <v>109</v>
       </c>
-      <c r="X19" t="s">
+      <c r="BI19" t="s">
         <v>109</v>
       </c>
-      <c r="Y19" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AB19" t="s">
+      <c r="BJ19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BK19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BL19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BM19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BN19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BO19" t="s">
         <v>109</v>
       </c>
-      <c r="AC19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AI19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AK19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AL19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AO19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AP19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AW19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AX19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AY19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AZ19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BA19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BB19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BC19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BE19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BF19" t="s">
-        <v>111</v>
-      </c>
-      <c r="BG19" t="s">
-        <v>111</v>
-      </c>
-      <c r="BH19" t="s">
-        <v>111</v>
-      </c>
-      <c r="BI19" t="s">
-        <v>111</v>
-      </c>
-      <c r="BJ19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BK19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BL19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BM19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BN19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BO19" t="s">
-        <v>111</v>
-      </c>
       <c r="BP19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BQ19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BR19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BS19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BT19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BU19" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV19" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW19" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5167,73 +5092,73 @@
         <v>108</v>
       </c>
       <c r="Q20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R20" t="s">
         <v>108</v>
       </c>
       <c r="S20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V20" t="s">
         <v>108</v>
       </c>
       <c r="W20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN20" t="s">
         <v>108</v>
@@ -5323,10 +5248,10 @@
         <v>108</v>
       </c>
       <c r="BQ20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BS20" t="s">
         <v>108</v>
@@ -5335,13 +5260,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BV20" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW20" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5355,88 +5280,88 @@
         <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G21" t="s">
         <v>108</v>
       </c>
       <c r="H21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M21" t="s">
         <v>108</v>
       </c>
       <c r="N21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O21" t="s">
         <v>108</v>
       </c>
       <c r="P21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF21" t="s">
         <v>108</v>
@@ -5448,10 +5373,10 @@
         <v>108</v>
       </c>
       <c r="AI21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK21" t="s">
         <v>108</v>
@@ -5562,13 +5487,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV21" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW21" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5606,7 +5531,7 @@
         <v>108</v>
       </c>
       <c r="L22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M22" t="s">
         <v>108</v>
@@ -5618,10 +5543,10 @@
         <v>108</v>
       </c>
       <c r="P22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R22" t="s">
         <v>108</v>
@@ -5630,55 +5555,55 @@
         <v>108</v>
       </c>
       <c r="T22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK22" t="s">
         <v>108</v>
@@ -5789,13 +5714,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV22" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5803,22 +5728,22 @@
         <v>96</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F23" t="s">
         <v>108</v>
       </c>
       <c r="G23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H23" t="s">
         <v>108</v>
@@ -5848,67 +5773,67 @@
         <v>108</v>
       </c>
       <c r="Q23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH23" t="s">
         <v>108</v>
       </c>
       <c r="AI23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL23" t="s">
         <v>108</v>
@@ -6016,13 +5941,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV23" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="BW23" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6078,67 +6003,67 @@
         <v>108</v>
       </c>
       <c r="R24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM24" t="s">
         <v>108</v>
@@ -6243,13 +6168,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV24" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BW24" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6299,70 +6224,70 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL25" t="s">
         <v>108</v>
@@ -6470,13 +6395,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BV25" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="BW25" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6514,10 +6439,10 @@
         <v>108</v>
       </c>
       <c r="L26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N26" t="s">
         <v>108</v>
@@ -6544,166 +6469,166 @@
         <v>108</v>
       </c>
       <c r="V26" t="s">
+        <v>108</v>
+      </c>
+      <c r="W26" t="s">
+        <v>108</v>
+      </c>
+      <c r="X26" t="s">
         <v>109</v>
       </c>
-      <c r="W26" t="s">
+      <c r="Y26" t="s">
         <v>109</v>
       </c>
-      <c r="X26" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>111</v>
-      </c>
       <c r="Z26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AD26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AL26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AN26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AO26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AP26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AQ26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AR26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AS26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AT26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AU26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AV26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AW26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AX26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AY26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AZ26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BA26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BB26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BC26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BD26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BE26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BF26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BG26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BH26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BI26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BJ26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BK26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BL26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BM26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BN26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BO26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BP26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BQ26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BR26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BS26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BT26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BU26" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="BV26" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BW26" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6711,16 +6636,16 @@
         <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F27" t="s">
         <v>108</v>
@@ -6729,10 +6654,10 @@
         <v>108</v>
       </c>
       <c r="H27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J27" t="s">
         <v>108</v>
@@ -6759,67 +6684,67 @@
         <v>108</v>
       </c>
       <c r="R27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM27" t="s">
         <v>108</v>
@@ -6924,13 +6849,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV27" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="BW27" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -6944,7 +6869,7 @@
         <v>108</v>
       </c>
       <c r="D28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
         <v>108</v>
@@ -6962,85 +6887,85 @@
         <v>108</v>
       </c>
       <c r="J28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K28" t="s">
         <v>108</v>
       </c>
       <c r="L28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK28" t="s">
         <v>108</v>
@@ -7151,13 +7076,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BV28" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW28" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7213,67 +7138,67 @@
         <v>108</v>
       </c>
       <c r="R29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="S29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM29" t="s">
         <v>108</v>
@@ -7282,7 +7207,7 @@
         <v>108</v>
       </c>
       <c r="AO29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AP29" t="s">
         <v>108</v>
@@ -7378,13 +7303,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV29" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BW29" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7443,61 +7368,61 @@
         <v>108</v>
       </c>
       <c r="S30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL30" t="s">
         <v>108</v>
@@ -7605,13 +7530,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV30" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BW30" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7676,70 +7601,70 @@
         <v>108</v>
       </c>
       <c r="U31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM31" t="s">
         <v>108</v>
       </c>
       <c r="AN31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO31" t="s">
         <v>108</v>
       </c>
       <c r="AP31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ31" t="s">
         <v>108</v>
@@ -7805,7 +7730,7 @@
         <v>108</v>
       </c>
       <c r="BL31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BM31" t="s">
         <v>108</v>
@@ -7832,13 +7757,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV31" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW31" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7846,7 +7771,7 @@
         <v>105</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
         <v>108</v>
@@ -7855,25 +7780,25 @@
         <v>108</v>
       </c>
       <c r="E32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L32" t="s">
         <v>108</v>
@@ -7882,73 +7807,73 @@
         <v>108</v>
       </c>
       <c r="N32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O32" t="s">
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK32" t="s">
         <v>108</v>
@@ -8059,13 +7984,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BV32" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW32" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8073,7 +7998,7 @@
         <v>106</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
         <v>108</v>
@@ -8133,73 +8058,73 @@
         <v>108</v>
       </c>
       <c r="V33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AN33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AS33" t="s">
         <v>108</v>
@@ -8286,13 +8211,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV33" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BW33" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8300,37 +8225,37 @@
         <v>107</v>
       </c>
       <c r="B34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H34" t="s">
         <v>108</v>
       </c>
       <c r="I34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M34" t="s">
         <v>108</v>
@@ -8345,7 +8270,7 @@
         <v>108</v>
       </c>
       <c r="Q34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R34" t="s">
         <v>108</v>
@@ -8357,55 +8282,55 @@
         <v>108</v>
       </c>
       <c r="U34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y34" t="s">
         <v>108</v>
       </c>
       <c r="Z34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL34" t="s">
         <v>108</v>
@@ -8513,13 +8438,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BV34" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW34" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ToT_(Labour/Cereal)_percentile_classification_matrix.xlsx
+++ b/outputs/ToT_(Labour/Cereal)_percentile_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
